--- a/artfynd/A 40978-2024 artfynd.xlsx
+++ b/artfynd/A 40978-2024 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121072585</v>
+        <v>121072562</v>
       </c>
       <c r="B4" t="n">
-        <v>90701</v>
+        <v>74710</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>1467</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545532</v>
+        <v>545531</v>
       </c>
       <c r="R4" t="n">
-        <v>7206858</v>
+        <v>7207026</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121072562</v>
+        <v>121072585</v>
       </c>
       <c r="B5" t="n">
-        <v>74710</v>
+        <v>90701</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1467</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545531</v>
+        <v>545532</v>
       </c>
       <c r="R5" t="n">
-        <v>7207026</v>
+        <v>7206858</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121072555</v>
+        <v>121072576</v>
       </c>
       <c r="B11" t="n">
-        <v>57348</v>
+        <v>90652</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1700,43 +1700,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545610</v>
+        <v>545540</v>
       </c>
       <c r="R11" t="n">
-        <v>7206991</v>
+        <v>7206902</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1768,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121072576</v>
+        <v>121072555</v>
       </c>
       <c r="B12" t="n">
-        <v>90652</v>
+        <v>57348</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1817,38 +1812,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545540</v>
+        <v>545610</v>
       </c>
       <c r="R12" t="n">
-        <v>7206902</v>
+        <v>7206991</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -3042,10 +3042,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121072559</v>
+        <v>121072590</v>
       </c>
       <c r="B23" t="n">
-        <v>57501</v>
+        <v>94474</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3054,42 +3054,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>2809</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545580</v>
+        <v>545506</v>
       </c>
       <c r="R23" t="n">
-        <v>7207025</v>
+        <v>7206868</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3121,7 +3117,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3131,7 +3127,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3158,10 +3154,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121072590</v>
+        <v>121072561</v>
       </c>
       <c r="B24" t="n">
-        <v>94474</v>
+        <v>78598</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3170,25 +3166,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3198,10 +3194,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545506</v>
+        <v>545577</v>
       </c>
       <c r="R24" t="n">
-        <v>7206868</v>
+        <v>7207030</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3233,7 +3229,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3243,7 +3239,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3270,10 +3266,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121072561</v>
+        <v>121072559</v>
       </c>
       <c r="B25" t="n">
-        <v>78598</v>
+        <v>57501</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3286,34 +3282,38 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>545577</v>
+        <v>545580</v>
       </c>
       <c r="R25" t="n">
-        <v>7207030</v>
+        <v>7207025</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -5066,10 +5066,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121072589</v>
+        <v>121072560</v>
       </c>
       <c r="B41" t="n">
-        <v>79708</v>
+        <v>78598</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5078,25 +5078,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>545508</v>
+        <v>545571</v>
       </c>
       <c r="R41" t="n">
-        <v>7206867</v>
+        <v>7207020</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5178,10 +5178,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121072560</v>
+        <v>121072589</v>
       </c>
       <c r="B42" t="n">
-        <v>78598</v>
+        <v>79708</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5190,25 +5190,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5218,10 +5218,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>545571</v>
+        <v>545508</v>
       </c>
       <c r="R42" t="n">
-        <v>7207020</v>
+        <v>7206867</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 40978-2024 artfynd.xlsx
+++ b/artfynd/A 40978-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121072557</v>
+        <v>121072593</v>
       </c>
       <c r="B2" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545608</v>
+        <v>545505</v>
       </c>
       <c r="R2" t="n">
-        <v>7206991</v>
+        <v>7206860</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121072586</v>
+        <v>121072577</v>
       </c>
       <c r="B3" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545532</v>
+        <v>545540</v>
       </c>
       <c r="R3" t="n">
-        <v>7206858</v>
+        <v>7206902</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121072562</v>
+        <v>121072570</v>
       </c>
       <c r="B4" t="n">
-        <v>74710</v>
+        <v>57462</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,38 +911,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1467</v>
+        <v>103031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545531</v>
+        <v>545597</v>
       </c>
       <c r="R4" t="n">
-        <v>7207026</v>
+        <v>7206943</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121072585</v>
+        <v>121072590</v>
       </c>
       <c r="B5" t="n">
-        <v>90701</v>
+        <v>94484</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,25 +1027,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1204</v>
+        <v>2809</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545532</v>
+        <v>545506</v>
       </c>
       <c r="R5" t="n">
-        <v>7206858</v>
+        <v>7206868</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121072567</v>
+        <v>121072583</v>
       </c>
       <c r="B6" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545533</v>
+        <v>545540</v>
       </c>
       <c r="R6" t="n">
-        <v>7207012</v>
+        <v>7206882</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121072579</v>
+        <v>121072586</v>
       </c>
       <c r="B7" t="n">
-        <v>79645</v>
+        <v>78601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,25 +1251,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545524</v>
+        <v>545532</v>
       </c>
       <c r="R7" t="n">
-        <v>7206894</v>
+        <v>7206858</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121072587</v>
+        <v>121072555</v>
       </c>
       <c r="B8" t="n">
-        <v>94486</v>
+        <v>57351</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,38 +1363,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2813</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545516</v>
+        <v>545610</v>
       </c>
       <c r="R8" t="n">
-        <v>7206861</v>
+        <v>7206991</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121072556</v>
+        <v>121072569</v>
       </c>
       <c r="B9" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545610</v>
+        <v>545526</v>
       </c>
       <c r="R9" t="n">
-        <v>7206991</v>
+        <v>7206990</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1539,7 +1543,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1553,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121072588</v>
+        <v>121072556</v>
       </c>
       <c r="B10" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545516</v>
+        <v>545610</v>
       </c>
       <c r="R10" t="n">
-        <v>7206861</v>
+        <v>7206991</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1651,7 +1655,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1665,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121072576</v>
+        <v>121072558</v>
       </c>
       <c r="B11" t="n">
-        <v>90652</v>
+        <v>78601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1700,25 +1704,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1728,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545540</v>
+        <v>545608</v>
       </c>
       <c r="R11" t="n">
-        <v>7206902</v>
+        <v>7206990</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1763,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1777,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,10 +1804,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121072555</v>
+        <v>121072561</v>
       </c>
       <c r="B12" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,39 +1820,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545610</v>
+        <v>545577</v>
       </c>
       <c r="R12" t="n">
-        <v>7206991</v>
+        <v>7207030</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1880,7 +1879,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1889,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121072591</v>
+        <v>121072552</v>
       </c>
       <c r="B13" t="n">
-        <v>97025</v>
+        <v>78601</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1929,25 +1928,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1957,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545503</v>
+        <v>545682</v>
       </c>
       <c r="R13" t="n">
-        <v>7206867</v>
+        <v>7206971</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1992,7 +1991,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +2001,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121072553</v>
+        <v>121072574</v>
       </c>
       <c r="B14" t="n">
-        <v>90683</v>
+        <v>78601</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,21 +2044,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2069,10 +2068,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545674</v>
+        <v>545534</v>
       </c>
       <c r="R14" t="n">
-        <v>7206979</v>
+        <v>7206903</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2104,7 +2103,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2113,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,10 +2140,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121072583</v>
+        <v>121072564</v>
       </c>
       <c r="B15" t="n">
-        <v>78598</v>
+        <v>74708</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2157,21 +2156,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2181,10 +2180,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545540</v>
+        <v>545530</v>
       </c>
       <c r="R15" t="n">
-        <v>7206882</v>
+        <v>7207028</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2216,7 +2215,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2226,7 +2225,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2253,10 +2252,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121072581</v>
+        <v>121072576</v>
       </c>
       <c r="B16" t="n">
-        <v>78598</v>
+        <v>90662</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2265,25 +2264,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2293,10 +2292,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545522</v>
+        <v>545540</v>
       </c>
       <c r="R16" t="n">
-        <v>7206880</v>
+        <v>7206902</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2328,7 +2327,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2338,7 +2337,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,10 +2364,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121072572</v>
+        <v>121072557</v>
       </c>
       <c r="B17" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2381,34 +2380,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545525</v>
+        <v>545608</v>
       </c>
       <c r="R17" t="n">
-        <v>7206961</v>
+        <v>7206991</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2440,7 +2444,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,7 +2454,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2477,10 +2481,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121072569</v>
+        <v>121072588</v>
       </c>
       <c r="B18" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2517,10 +2521,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545526</v>
+        <v>545516</v>
       </c>
       <c r="R18" t="n">
-        <v>7206990</v>
+        <v>7206861</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2552,7 +2556,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2562,7 +2566,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,10 +2593,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121072554</v>
+        <v>121072560</v>
       </c>
       <c r="B19" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2629,10 +2633,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545672</v>
+        <v>545571</v>
       </c>
       <c r="R19" t="n">
-        <v>7206977</v>
+        <v>7207020</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2664,7 +2668,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2674,7 +2678,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2701,10 +2705,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121072573</v>
+        <v>121072566</v>
       </c>
       <c r="B20" t="n">
-        <v>57348</v>
+        <v>90697</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2717,39 +2721,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545534</v>
+        <v>545532</v>
       </c>
       <c r="R20" t="n">
-        <v>7206903</v>
+        <v>7207020</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2781,7 +2780,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2791,7 +2790,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2821,7 +2820,7 @@
         <v>121072563</v>
       </c>
       <c r="B21" t="n">
-        <v>77535</v>
+        <v>77538</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2930,10 +2929,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121072578</v>
+        <v>121072559</v>
       </c>
       <c r="B22" t="n">
-        <v>78598</v>
+        <v>57504</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2946,34 +2945,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545524</v>
+        <v>545580</v>
       </c>
       <c r="R22" t="n">
-        <v>7206893</v>
+        <v>7207025</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3005,7 +3008,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3015,7 +3018,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3042,10 +3045,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121072590</v>
+        <v>121072582</v>
       </c>
       <c r="B23" t="n">
-        <v>94474</v>
+        <v>74706</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3054,25 +3057,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2809</v>
+        <v>6486</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3082,10 +3085,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545506</v>
+        <v>545540</v>
       </c>
       <c r="R23" t="n">
-        <v>7206868</v>
+        <v>7206883</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3117,7 +3120,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3127,7 +3130,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3154,10 +3157,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121072561</v>
+        <v>121072567</v>
       </c>
       <c r="B24" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3194,10 +3197,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545577</v>
+        <v>545533</v>
       </c>
       <c r="R24" t="n">
-        <v>7207030</v>
+        <v>7207012</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3229,7 +3232,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3239,7 +3242,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3266,10 +3269,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121072559</v>
+        <v>121072565</v>
       </c>
       <c r="B25" t="n">
-        <v>57501</v>
+        <v>78601</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3282,38 +3285,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>545580</v>
+        <v>545527</v>
       </c>
       <c r="R25" t="n">
-        <v>7207025</v>
+        <v>7207023</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3345,7 +3344,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3355,7 +3354,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3382,10 +3381,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121072571</v>
+        <v>121072579</v>
       </c>
       <c r="B26" t="n">
-        <v>77535</v>
+        <v>79648</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3394,25 +3393,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228579</v>
+        <v>229748</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3425,7 +3424,7 @@
         <v>545524</v>
       </c>
       <c r="R26" t="n">
-        <v>7206961</v>
+        <v>7206894</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3457,7 +3456,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3467,7 +3466,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3494,10 +3493,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121072570</v>
+        <v>121072580</v>
       </c>
       <c r="B27" t="n">
-        <v>57459</v>
+        <v>79711</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3510,38 +3509,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103031</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>545597</v>
+        <v>545525</v>
       </c>
       <c r="R27" t="n">
-        <v>7206943</v>
+        <v>7206894</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3573,7 +3568,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3583,7 +3578,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3610,10 +3605,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121072575</v>
+        <v>121072585</v>
       </c>
       <c r="B28" t="n">
-        <v>90701</v>
+        <v>90711</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3650,10 +3645,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>545534</v>
+        <v>545532</v>
       </c>
       <c r="R28" t="n">
-        <v>7206899</v>
+        <v>7206858</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3685,7 +3680,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3695,7 +3690,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3722,10 +3717,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121072552</v>
+        <v>121072575</v>
       </c>
       <c r="B29" t="n">
-        <v>78598</v>
+        <v>90711</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3738,21 +3733,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3762,10 +3757,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>545682</v>
+        <v>545534</v>
       </c>
       <c r="R29" t="n">
-        <v>7206971</v>
+        <v>7206899</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3797,7 +3792,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3807,7 +3802,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3834,10 +3829,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121072565</v>
+        <v>121072554</v>
       </c>
       <c r="B30" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3874,10 +3869,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>545527</v>
+        <v>545672</v>
       </c>
       <c r="R30" t="n">
-        <v>7207023</v>
+        <v>7206977</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3909,7 +3904,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3919,7 +3914,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3946,10 +3941,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121072566</v>
+        <v>121072587</v>
       </c>
       <c r="B31" t="n">
-        <v>90687</v>
+        <v>94496</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3958,25 +3953,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>2813</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3986,10 +3981,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>545532</v>
+        <v>545516</v>
       </c>
       <c r="R31" t="n">
-        <v>7207020</v>
+        <v>7206861</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4021,7 +4016,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4031,7 +4026,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4058,10 +4053,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121072551</v>
+        <v>121072572</v>
       </c>
       <c r="B32" t="n">
-        <v>91370</v>
+        <v>78601</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4070,25 +4065,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4098,10 +4093,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>545676</v>
+        <v>545525</v>
       </c>
       <c r="R32" t="n">
-        <v>7206979</v>
+        <v>7206961</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4133,7 +4128,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4143,7 +4138,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4170,10 +4165,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121072558</v>
+        <v>121072578</v>
       </c>
       <c r="B33" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4210,10 +4205,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>545608</v>
+        <v>545524</v>
       </c>
       <c r="R33" t="n">
-        <v>7206990</v>
+        <v>7206893</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4245,7 +4240,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4255,7 +4250,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4282,10 +4277,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121072574</v>
+        <v>121072571</v>
       </c>
       <c r="B34" t="n">
-        <v>78598</v>
+        <v>77538</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4298,21 +4293,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4322,10 +4317,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>545534</v>
+        <v>545524</v>
       </c>
       <c r="R34" t="n">
-        <v>7206903</v>
+        <v>7206961</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4357,7 +4352,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4367,7 +4362,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4394,10 +4389,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121072564</v>
+        <v>121072589</v>
       </c>
       <c r="B35" t="n">
-        <v>74705</v>
+        <v>79711</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4406,25 +4401,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4434,10 +4429,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>545530</v>
+        <v>545508</v>
       </c>
       <c r="R35" t="n">
-        <v>7207028</v>
+        <v>7206867</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4469,7 +4464,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4479,7 +4474,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4506,10 +4501,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121072593</v>
+        <v>121072553</v>
       </c>
       <c r="B36" t="n">
-        <v>78598</v>
+        <v>90693</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4522,21 +4517,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4546,10 +4541,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>545505</v>
+        <v>545674</v>
       </c>
       <c r="R36" t="n">
-        <v>7206860</v>
+        <v>7206979</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4581,7 +4576,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4591,7 +4586,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4618,10 +4613,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121072582</v>
+        <v>121072581</v>
       </c>
       <c r="B37" t="n">
-        <v>74703</v>
+        <v>78601</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4630,25 +4625,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4658,10 +4653,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>545540</v>
+        <v>545522</v>
       </c>
       <c r="R37" t="n">
-        <v>7206883</v>
+        <v>7206880</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4693,7 +4688,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4703,7 +4698,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4730,10 +4725,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121072592</v>
+        <v>121072591</v>
       </c>
       <c r="B38" t="n">
-        <v>91620</v>
+        <v>97035</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4746,21 +4741,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4769</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4770,10 +4765,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>545502</v>
+        <v>545503</v>
       </c>
       <c r="R38" t="n">
-        <v>7206865</v>
+        <v>7206867</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4842,10 +4837,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121072580</v>
+        <v>121072562</v>
       </c>
       <c r="B39" t="n">
-        <v>79708</v>
+        <v>74713</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4854,25 +4849,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>1467</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4882,10 +4877,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>545525</v>
+        <v>545531</v>
       </c>
       <c r="R39" t="n">
-        <v>7206894</v>
+        <v>7207026</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4917,7 +4912,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4927,7 +4922,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4954,10 +4949,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121072577</v>
+        <v>121072592</v>
       </c>
       <c r="B40" t="n">
-        <v>78598</v>
+        <v>91630</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4966,25 +4961,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4994,10 +4989,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>545540</v>
+        <v>545502</v>
       </c>
       <c r="R40" t="n">
-        <v>7206902</v>
+        <v>7206865</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5029,7 +5024,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5039,7 +5034,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5066,10 +5061,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121072560</v>
+        <v>121072551</v>
       </c>
       <c r="B41" t="n">
-        <v>78598</v>
+        <v>91380</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5078,25 +5073,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5106,10 +5101,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>545571</v>
+        <v>545676</v>
       </c>
       <c r="R41" t="n">
-        <v>7207020</v>
+        <v>7206979</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5141,7 +5136,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5151,7 +5146,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5178,10 +5173,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121072589</v>
+        <v>121072573</v>
       </c>
       <c r="B42" t="n">
-        <v>79708</v>
+        <v>57351</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5190,38 +5185,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>545508</v>
+        <v>545534</v>
       </c>
       <c r="R42" t="n">
-        <v>7206867</v>
+        <v>7206903</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 40978-2024 artfynd.xlsx
+++ b/artfynd/A 40978-2024 artfynd.xlsx
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121072590</v>
+        <v>121072583</v>
       </c>
       <c r="B5" t="n">
-        <v>94484</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,25 +1027,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545506</v>
+        <v>545540</v>
       </c>
       <c r="R5" t="n">
-        <v>7206868</v>
+        <v>7206882</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121072583</v>
+        <v>121072590</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>94484</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,25 +1139,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545540</v>
+        <v>545506</v>
       </c>
       <c r="R6" t="n">
-        <v>7206882</v>
+        <v>7206868</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1468,7 +1468,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121072569</v>
+        <v>121072556</v>
       </c>
       <c r="B9" t="n">
         <v>78601</v>
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545526</v>
+        <v>545610</v>
       </c>
       <c r="R9" t="n">
-        <v>7206990</v>
+        <v>7206991</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,7 +1580,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121072556</v>
+        <v>121072569</v>
       </c>
       <c r="B10" t="n">
         <v>78601</v>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545610</v>
+        <v>545526</v>
       </c>
       <c r="R10" t="n">
-        <v>7206991</v>
+        <v>7206990</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2705,10 +2705,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121072566</v>
+        <v>121072563</v>
       </c>
       <c r="B20" t="n">
-        <v>90697</v>
+        <v>77538</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2721,21 +2721,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545532</v>
+        <v>545530</v>
       </c>
       <c r="R20" t="n">
-        <v>7207020</v>
+        <v>7207027</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2817,10 +2817,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121072563</v>
+        <v>121072566</v>
       </c>
       <c r="B21" t="n">
-        <v>77538</v>
+        <v>90697</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2833,21 +2833,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545530</v>
+        <v>545532</v>
       </c>
       <c r="R21" t="n">
-        <v>7207027</v>
+        <v>7207020</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2929,10 +2929,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121072559</v>
+        <v>121072582</v>
       </c>
       <c r="B22" t="n">
-        <v>57504</v>
+        <v>74706</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2941,42 +2941,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6486</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545580</v>
+        <v>545540</v>
       </c>
       <c r="R22" t="n">
-        <v>7207025</v>
+        <v>7206883</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3008,7 +3004,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3018,7 +3014,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3045,10 +3041,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121072582</v>
+        <v>121072559</v>
       </c>
       <c r="B23" t="n">
-        <v>74706</v>
+        <v>57504</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3057,38 +3053,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6486</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Nádv.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545540</v>
+        <v>545580</v>
       </c>
       <c r="R23" t="n">
-        <v>7206883</v>
+        <v>7207025</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3829,10 +3829,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121072554</v>
+        <v>121072587</v>
       </c>
       <c r="B30" t="n">
-        <v>78601</v>
+        <v>94496</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3841,25 +3841,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>2813</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3869,10 +3869,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>545672</v>
+        <v>545516</v>
       </c>
       <c r="R30" t="n">
-        <v>7206977</v>
+        <v>7206861</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3941,10 +3941,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121072587</v>
+        <v>121072554</v>
       </c>
       <c r="B31" t="n">
-        <v>94496</v>
+        <v>78601</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3953,25 +3953,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2813</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>545516</v>
+        <v>545672</v>
       </c>
       <c r="R31" t="n">
-        <v>7206861</v>
+        <v>7206977</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4501,10 +4501,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121072553</v>
+        <v>121072581</v>
       </c>
       <c r="B36" t="n">
-        <v>90693</v>
+        <v>78601</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4517,21 +4517,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4541,10 +4541,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>545674</v>
+        <v>545522</v>
       </c>
       <c r="R36" t="n">
-        <v>7206979</v>
+        <v>7206880</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4613,10 +4613,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121072581</v>
+        <v>121072553</v>
       </c>
       <c r="B37" t="n">
-        <v>78601</v>
+        <v>90693</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4629,21 +4629,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>545522</v>
+        <v>545674</v>
       </c>
       <c r="R37" t="n">
-        <v>7206880</v>
+        <v>7206979</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4688,7 +4688,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 40978-2024 artfynd.xlsx
+++ b/artfynd/A 40978-2024 artfynd.xlsx
@@ -2140,10 +2140,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121072564</v>
+        <v>121072576</v>
       </c>
       <c r="B15" t="n">
-        <v>74708</v>
+        <v>90662</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,25 +2152,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545530</v>
+        <v>545540</v>
       </c>
       <c r="R15" t="n">
-        <v>7207028</v>
+        <v>7206902</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2252,10 +2252,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121072576</v>
+        <v>121072588</v>
       </c>
       <c r="B16" t="n">
-        <v>90662</v>
+        <v>78601</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,25 +2264,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545540</v>
+        <v>545516</v>
       </c>
       <c r="R16" t="n">
-        <v>7206902</v>
+        <v>7206861</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2481,10 +2481,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121072588</v>
+        <v>121072564</v>
       </c>
       <c r="B18" t="n">
-        <v>78601</v>
+        <v>74708</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2497,21 +2497,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545516</v>
+        <v>545530</v>
       </c>
       <c r="R18" t="n">
-        <v>7206861</v>
+        <v>7207028</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2705,10 +2705,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121072563</v>
+        <v>121072566</v>
       </c>
       <c r="B20" t="n">
-        <v>77538</v>
+        <v>90697</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2721,21 +2721,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545530</v>
+        <v>545532</v>
       </c>
       <c r="R20" t="n">
-        <v>7207027</v>
+        <v>7207020</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2817,10 +2817,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121072566</v>
+        <v>121072563</v>
       </c>
       <c r="B21" t="n">
-        <v>90697</v>
+        <v>77538</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2833,21 +2833,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545532</v>
+        <v>545530</v>
       </c>
       <c r="R21" t="n">
-        <v>7207020</v>
+        <v>7207027</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3829,10 +3829,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121072587</v>
+        <v>121072554</v>
       </c>
       <c r="B30" t="n">
-        <v>94496</v>
+        <v>78601</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3841,25 +3841,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2813</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3869,10 +3869,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>545516</v>
+        <v>545672</v>
       </c>
       <c r="R30" t="n">
-        <v>7206861</v>
+        <v>7206977</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3941,10 +3941,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121072554</v>
+        <v>121072587</v>
       </c>
       <c r="B31" t="n">
-        <v>78601</v>
+        <v>94496</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3953,25 +3953,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2813</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>545672</v>
+        <v>545516</v>
       </c>
       <c r="R31" t="n">
-        <v>7206977</v>
+        <v>7206861</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4501,10 +4501,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121072581</v>
+        <v>121072553</v>
       </c>
       <c r="B36" t="n">
-        <v>78601</v>
+        <v>90693</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4517,21 +4517,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4541,10 +4541,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>545522</v>
+        <v>545674</v>
       </c>
       <c r="R36" t="n">
-        <v>7206880</v>
+        <v>7206979</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4613,10 +4613,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121072553</v>
+        <v>121072581</v>
       </c>
       <c r="B37" t="n">
-        <v>90693</v>
+        <v>78601</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4629,21 +4629,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>545674</v>
+        <v>545522</v>
       </c>
       <c r="R37" t="n">
-        <v>7206979</v>
+        <v>7206880</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4688,7 +4688,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 40978-2024 artfynd.xlsx
+++ b/artfynd/A 40978-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121072593</v>
+        <v>121072575</v>
       </c>
       <c r="B2" t="n">
-        <v>78601</v>
+        <v>90711</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545505</v>
+        <v>545534</v>
       </c>
       <c r="R2" t="n">
-        <v>7206860</v>
+        <v>7206899</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121072577</v>
+        <v>121072578</v>
       </c>
       <c r="B3" t="n">
         <v>78601</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545540</v>
+        <v>545524</v>
       </c>
       <c r="R3" t="n">
-        <v>7206902</v>
+        <v>7206893</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121072570</v>
+        <v>121072588</v>
       </c>
       <c r="B4" t="n">
-        <v>57462</v>
+        <v>78601</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,42 +911,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545597</v>
+        <v>545516</v>
       </c>
       <c r="R4" t="n">
-        <v>7206943</v>
+        <v>7206861</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121072583</v>
+        <v>121072563</v>
       </c>
       <c r="B5" t="n">
-        <v>78601</v>
+        <v>77538</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545540</v>
+        <v>545530</v>
       </c>
       <c r="R5" t="n">
-        <v>7206882</v>
+        <v>7207027</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1090,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121072590</v>
+        <v>121072571</v>
       </c>
       <c r="B6" t="n">
-        <v>94484</v>
+        <v>77538</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2809</v>
+        <v>228579</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545506</v>
+        <v>545524</v>
       </c>
       <c r="R6" t="n">
-        <v>7206868</v>
+        <v>7206961</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1202,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121072586</v>
+        <v>121072555</v>
       </c>
       <c r="B7" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,34 +1251,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545532</v>
+        <v>545610</v>
       </c>
       <c r="R7" t="n">
-        <v>7206858</v>
+        <v>7206991</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1314,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1324,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121072555</v>
+        <v>121072590</v>
       </c>
       <c r="B8" t="n">
-        <v>57351</v>
+        <v>94484</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,43 +1364,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545610</v>
+        <v>545506</v>
       </c>
       <c r="R8" t="n">
-        <v>7206991</v>
+        <v>7206868</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1431,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121072556</v>
+        <v>121072553</v>
       </c>
       <c r="B9" t="n">
-        <v>78601</v>
+        <v>90693</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545610</v>
+        <v>545674</v>
       </c>
       <c r="R9" t="n">
-        <v>7206991</v>
+        <v>7206979</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1543,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1553,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,7 +1576,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121072569</v>
+        <v>121072552</v>
       </c>
       <c r="B10" t="n">
         <v>78601</v>
@@ -1620,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545526</v>
+        <v>545682</v>
       </c>
       <c r="R10" t="n">
-        <v>7206990</v>
+        <v>7206971</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1655,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1665,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,7 +1688,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121072558</v>
+        <v>121072583</v>
       </c>
       <c r="B11" t="n">
         <v>78601</v>
@@ -1732,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545608</v>
+        <v>545540</v>
       </c>
       <c r="R11" t="n">
-        <v>7206990</v>
+        <v>7206882</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1767,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,7 +1800,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121072561</v>
+        <v>121072565</v>
       </c>
       <c r="B12" t="n">
         <v>78601</v>
@@ -1844,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545577</v>
+        <v>545527</v>
       </c>
       <c r="R12" t="n">
-        <v>7207030</v>
+        <v>7207023</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1879,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1889,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,7 +1912,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121072552</v>
+        <v>121072581</v>
       </c>
       <c r="B13" t="n">
         <v>78601</v>
@@ -1956,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545682</v>
+        <v>545522</v>
       </c>
       <c r="R13" t="n">
-        <v>7206971</v>
+        <v>7206880</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1991,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2001,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121072574</v>
+        <v>121072582</v>
       </c>
       <c r="B14" t="n">
-        <v>78601</v>
+        <v>74706</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,25 +2036,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2068,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545534</v>
+        <v>545540</v>
       </c>
       <c r="R14" t="n">
-        <v>7206903</v>
+        <v>7206883</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2103,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2113,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121072576</v>
+        <v>121072558</v>
       </c>
       <c r="B15" t="n">
-        <v>90662</v>
+        <v>78601</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,25 +2148,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2180,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545540</v>
+        <v>545608</v>
       </c>
       <c r="R15" t="n">
-        <v>7206902</v>
+        <v>7206990</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2215,7 +2211,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2225,7 +2221,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2252,7 +2248,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121072588</v>
+        <v>121072572</v>
       </c>
       <c r="B16" t="n">
         <v>78601</v>
@@ -2292,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545516</v>
+        <v>545525</v>
       </c>
       <c r="R16" t="n">
-        <v>7206861</v>
+        <v>7206961</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2327,7 +2323,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2337,7 +2333,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2364,10 +2360,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121072557</v>
+        <v>121072579</v>
       </c>
       <c r="B17" t="n">
-        <v>57351</v>
+        <v>79648</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2376,43 +2372,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>229748</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545608</v>
+        <v>545524</v>
       </c>
       <c r="R17" t="n">
-        <v>7206991</v>
+        <v>7206894</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2444,7 +2435,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2454,7 +2445,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2481,10 +2472,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121072564</v>
+        <v>121072576</v>
       </c>
       <c r="B18" t="n">
-        <v>74708</v>
+        <v>90662</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2493,25 +2484,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2521,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545530</v>
+        <v>545540</v>
       </c>
       <c r="R18" t="n">
-        <v>7207028</v>
+        <v>7206902</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2556,7 +2547,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2566,7 +2557,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2593,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121072560</v>
+        <v>121072592</v>
       </c>
       <c r="B19" t="n">
-        <v>78601</v>
+        <v>91630</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2605,25 +2596,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2633,10 +2624,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545571</v>
+        <v>545502</v>
       </c>
       <c r="R19" t="n">
-        <v>7207020</v>
+        <v>7206865</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2668,7 +2659,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2678,7 +2669,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2705,10 +2696,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121072566</v>
+        <v>121072564</v>
       </c>
       <c r="B20" t="n">
-        <v>90697</v>
+        <v>74708</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2721,21 +2712,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2745,10 +2736,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545532</v>
+        <v>545530</v>
       </c>
       <c r="R20" t="n">
-        <v>7207020</v>
+        <v>7207028</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2780,7 +2771,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2790,7 +2781,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2817,10 +2808,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121072563</v>
+        <v>121072557</v>
       </c>
       <c r="B21" t="n">
-        <v>77538</v>
+        <v>57351</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2833,34 +2824,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545530</v>
+        <v>545608</v>
       </c>
       <c r="R21" t="n">
-        <v>7207027</v>
+        <v>7206991</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2892,7 +2888,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2902,7 +2898,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2929,10 +2925,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121072582</v>
+        <v>121072551</v>
       </c>
       <c r="B22" t="n">
-        <v>74706</v>
+        <v>91380</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2941,25 +2937,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6486</v>
+        <v>3298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2969,10 +2965,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545540</v>
+        <v>545676</v>
       </c>
       <c r="R22" t="n">
-        <v>7206883</v>
+        <v>7206979</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3004,7 +3000,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3014,7 +3010,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3041,10 +3037,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121072559</v>
+        <v>121072554</v>
       </c>
       <c r="B23" t="n">
-        <v>57504</v>
+        <v>78601</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3057,38 +3053,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545580</v>
+        <v>545672</v>
       </c>
       <c r="R23" t="n">
-        <v>7207025</v>
+        <v>7206977</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3120,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3130,7 +3122,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3157,10 +3149,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121072567</v>
+        <v>121072580</v>
       </c>
       <c r="B24" t="n">
-        <v>78601</v>
+        <v>79711</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3169,25 +3161,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3197,10 +3189,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545533</v>
+        <v>545525</v>
       </c>
       <c r="R24" t="n">
-        <v>7207012</v>
+        <v>7206894</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3232,7 +3224,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3242,7 +3234,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3269,7 +3261,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121072565</v>
+        <v>121072556</v>
       </c>
       <c r="B25" t="n">
         <v>78601</v>
@@ -3309,10 +3301,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>545527</v>
+        <v>545610</v>
       </c>
       <c r="R25" t="n">
-        <v>7207023</v>
+        <v>7206991</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3344,7 +3336,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3354,7 +3346,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3381,10 +3373,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121072579</v>
+        <v>121072587</v>
       </c>
       <c r="B26" t="n">
-        <v>79648</v>
+        <v>94496</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3397,21 +3389,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229748</v>
+        <v>2813</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3421,10 +3413,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>545524</v>
+        <v>545516</v>
       </c>
       <c r="R26" t="n">
-        <v>7206894</v>
+        <v>7206861</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3456,7 +3448,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3466,7 +3458,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3493,10 +3485,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121072580</v>
+        <v>121072562</v>
       </c>
       <c r="B27" t="n">
-        <v>79711</v>
+        <v>74713</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3505,25 +3497,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>1467</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3533,10 +3525,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>545525</v>
+        <v>545531</v>
       </c>
       <c r="R27" t="n">
-        <v>7206894</v>
+        <v>7207026</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3568,7 +3560,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3578,7 +3570,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3605,10 +3597,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121072585</v>
+        <v>121072593</v>
       </c>
       <c r="B28" t="n">
-        <v>90711</v>
+        <v>78601</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3621,21 +3613,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3645,10 +3637,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>545532</v>
+        <v>545505</v>
       </c>
       <c r="R28" t="n">
-        <v>7206858</v>
+        <v>7206860</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3680,7 +3672,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3690,7 +3682,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3717,10 +3709,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121072575</v>
+        <v>121072577</v>
       </c>
       <c r="B29" t="n">
-        <v>90711</v>
+        <v>78601</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3733,21 +3725,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3757,10 +3749,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>545534</v>
+        <v>545540</v>
       </c>
       <c r="R29" t="n">
-        <v>7206899</v>
+        <v>7206902</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3829,10 +3821,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121072554</v>
+        <v>121072589</v>
       </c>
       <c r="B30" t="n">
-        <v>78601</v>
+        <v>79711</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3841,25 +3833,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3869,10 +3861,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>545672</v>
+        <v>545508</v>
       </c>
       <c r="R30" t="n">
-        <v>7206977</v>
+        <v>7206867</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3904,7 +3896,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3914,7 +3906,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3941,10 +3933,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121072587</v>
+        <v>121072567</v>
       </c>
       <c r="B31" t="n">
-        <v>94496</v>
+        <v>78601</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3953,25 +3945,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2813</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3981,10 +3973,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>545516</v>
+        <v>545533</v>
       </c>
       <c r="R31" t="n">
-        <v>7206861</v>
+        <v>7207012</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4016,7 +4008,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4026,7 +4018,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4053,7 +4045,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121072572</v>
+        <v>121072586</v>
       </c>
       <c r="B32" t="n">
         <v>78601</v>
@@ -4093,10 +4085,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>545525</v>
+        <v>545532</v>
       </c>
       <c r="R32" t="n">
-        <v>7206961</v>
+        <v>7206858</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4128,7 +4120,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4138,7 +4130,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4165,10 +4157,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121072578</v>
+        <v>121072559</v>
       </c>
       <c r="B33" t="n">
-        <v>78601</v>
+        <v>57504</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4181,34 +4173,38 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>545524</v>
+        <v>545580</v>
       </c>
       <c r="R33" t="n">
-        <v>7206893</v>
+        <v>7207025</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4240,7 +4236,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4250,7 +4246,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4277,10 +4273,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121072571</v>
+        <v>121072566</v>
       </c>
       <c r="B34" t="n">
-        <v>77538</v>
+        <v>90697</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4293,21 +4289,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4317,10 +4313,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>545524</v>
+        <v>545532</v>
       </c>
       <c r="R34" t="n">
-        <v>7206961</v>
+        <v>7207020</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4352,7 +4348,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4362,7 +4358,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4389,10 +4385,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121072589</v>
+        <v>121072585</v>
       </c>
       <c r="B35" t="n">
-        <v>79711</v>
+        <v>90711</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4401,25 +4397,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4429,10 +4425,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>545508</v>
+        <v>545532</v>
       </c>
       <c r="R35" t="n">
-        <v>7206867</v>
+        <v>7206858</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4464,7 +4460,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4474,7 +4470,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4501,10 +4497,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121072553</v>
+        <v>121072560</v>
       </c>
       <c r="B36" t="n">
-        <v>90693</v>
+        <v>78601</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4517,21 +4513,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4541,10 +4537,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>545674</v>
+        <v>545571</v>
       </c>
       <c r="R36" t="n">
-        <v>7206979</v>
+        <v>7207020</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4576,7 +4572,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4586,7 +4582,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4613,7 +4609,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121072581</v>
+        <v>121072569</v>
       </c>
       <c r="B37" t="n">
         <v>78601</v>
@@ -4653,10 +4649,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>545522</v>
+        <v>545526</v>
       </c>
       <c r="R37" t="n">
-        <v>7206880</v>
+        <v>7206990</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4688,7 +4684,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4698,7 +4694,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4725,10 +4721,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121072591</v>
+        <v>121072561</v>
       </c>
       <c r="B38" t="n">
-        <v>97035</v>
+        <v>78601</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4737,25 +4733,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4765,10 +4761,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>545503</v>
+        <v>545577</v>
       </c>
       <c r="R38" t="n">
-        <v>7206867</v>
+        <v>7207030</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4800,7 +4796,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4810,7 +4806,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4837,10 +4833,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121072562</v>
+        <v>121072574</v>
       </c>
       <c r="B39" t="n">
-        <v>74713</v>
+        <v>78601</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4853,21 +4849,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4877,10 +4873,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>545531</v>
+        <v>545534</v>
       </c>
       <c r="R39" t="n">
-        <v>7207026</v>
+        <v>7206903</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4912,7 +4908,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4922,7 +4918,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4949,10 +4945,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121072592</v>
+        <v>121072573</v>
       </c>
       <c r="B40" t="n">
-        <v>91630</v>
+        <v>57351</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4961,38 +4957,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>545502</v>
+        <v>545534</v>
       </c>
       <c r="R40" t="n">
-        <v>7206865</v>
+        <v>7206903</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5024,7 +5025,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5034,7 +5035,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5061,10 +5062,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121072551</v>
+        <v>121072570</v>
       </c>
       <c r="B41" t="n">
-        <v>91380</v>
+        <v>57462</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5077,34 +5078,38 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3298</v>
+        <v>103031</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>545676</v>
+        <v>545597</v>
       </c>
       <c r="R41" t="n">
-        <v>7206979</v>
+        <v>7206943</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5136,7 +5141,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5146,7 +5151,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5173,10 +5178,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121072573</v>
+        <v>121072591</v>
       </c>
       <c r="B42" t="n">
-        <v>57351</v>
+        <v>97035</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5185,43 +5190,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>545534</v>
+        <v>545503</v>
       </c>
       <c r="R42" t="n">
-        <v>7206903</v>
+        <v>7206867</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 40978-2024 artfynd.xlsx
+++ b/artfynd/A 40978-2024 artfynd.xlsx
@@ -3261,10 +3261,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121072556</v>
+        <v>121072587</v>
       </c>
       <c r="B25" t="n">
-        <v>78601</v>
+        <v>94496</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3273,25 +3273,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2813</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>545610</v>
+        <v>545516</v>
       </c>
       <c r="R25" t="n">
-        <v>7206991</v>
+        <v>7206861</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3373,10 +3373,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121072587</v>
+        <v>121072556</v>
       </c>
       <c r="B26" t="n">
-        <v>94496</v>
+        <v>78601</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3385,25 +3385,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2813</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3413,10 +3413,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>545516</v>
+        <v>545610</v>
       </c>
       <c r="R26" t="n">
-        <v>7206861</v>
+        <v>7206991</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 40978-2024 artfynd.xlsx
+++ b/artfynd/A 40978-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121072575</v>
+        <v>121072576</v>
       </c>
       <c r="B2" t="n">
-        <v>90711</v>
+        <v>90674</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545534</v>
+        <v>545540</v>
       </c>
       <c r="R2" t="n">
-        <v>7206899</v>
+        <v>7206902</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121072578</v>
+        <v>121072581</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545524</v>
+        <v>545522</v>
       </c>
       <c r="R3" t="n">
-        <v>7206893</v>
+        <v>7206880</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121072588</v>
+        <v>121072553</v>
       </c>
       <c r="B4" t="n">
-        <v>78601</v>
+        <v>90705</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545516</v>
+        <v>545674</v>
       </c>
       <c r="R4" t="n">
-        <v>7206861</v>
+        <v>7206979</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121072563</v>
+        <v>121072555</v>
       </c>
       <c r="B5" t="n">
-        <v>77538</v>
+        <v>57351</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1027,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545530</v>
+        <v>545610</v>
       </c>
       <c r="R5" t="n">
-        <v>7207027</v>
+        <v>7206991</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121072571</v>
+        <v>121072551</v>
       </c>
       <c r="B6" t="n">
-        <v>77538</v>
+        <v>91392</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1140,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228579</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545524</v>
+        <v>545676</v>
       </c>
       <c r="R6" t="n">
-        <v>7206961</v>
+        <v>7206979</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121072555</v>
+        <v>121072591</v>
       </c>
       <c r="B7" t="n">
-        <v>57351</v>
+        <v>97048</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,43 +1252,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545610</v>
+        <v>545503</v>
       </c>
       <c r="R7" t="n">
-        <v>7206991</v>
+        <v>7206867</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121072590</v>
+        <v>121072575</v>
       </c>
       <c r="B8" t="n">
-        <v>94484</v>
+        <v>90723</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,25 +1364,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2809</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545506</v>
+        <v>545534</v>
       </c>
       <c r="R8" t="n">
-        <v>7206868</v>
+        <v>7206899</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121072553</v>
+        <v>121072558</v>
       </c>
       <c r="B9" t="n">
-        <v>90693</v>
+        <v>78604</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545674</v>
+        <v>545608</v>
       </c>
       <c r="R9" t="n">
-        <v>7206979</v>
+        <v>7206990</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121072552</v>
+        <v>121072588</v>
       </c>
       <c r="B10" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545682</v>
+        <v>545516</v>
       </c>
       <c r="R10" t="n">
-        <v>7206971</v>
+        <v>7206861</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121072583</v>
+        <v>121072562</v>
       </c>
       <c r="B11" t="n">
-        <v>78601</v>
+        <v>74715</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,21 +1704,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545540</v>
+        <v>545531</v>
       </c>
       <c r="R11" t="n">
-        <v>7206882</v>
+        <v>7207026</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121072565</v>
+        <v>121072556</v>
       </c>
       <c r="B12" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545527</v>
+        <v>545610</v>
       </c>
       <c r="R12" t="n">
-        <v>7207023</v>
+        <v>7206991</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121072581</v>
+        <v>121072589</v>
       </c>
       <c r="B13" t="n">
-        <v>78601</v>
+        <v>79714</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1924,25 +1924,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545522</v>
+        <v>545508</v>
       </c>
       <c r="R13" t="n">
-        <v>7206880</v>
+        <v>7206867</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121072582</v>
+        <v>121072567</v>
       </c>
       <c r="B14" t="n">
-        <v>74706</v>
+        <v>78604</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,25 +2036,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545540</v>
+        <v>545533</v>
       </c>
       <c r="R14" t="n">
-        <v>7206883</v>
+        <v>7207012</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121072558</v>
+        <v>121072569</v>
       </c>
       <c r="B15" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545608</v>
+        <v>545526</v>
       </c>
       <c r="R15" t="n">
         <v>7206990</v>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121072572</v>
+        <v>121072592</v>
       </c>
       <c r="B16" t="n">
-        <v>78601</v>
+        <v>91642</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2260,25 +2260,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545525</v>
+        <v>545502</v>
       </c>
       <c r="R16" t="n">
-        <v>7206961</v>
+        <v>7206865</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2360,10 +2360,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121072579</v>
+        <v>121072566</v>
       </c>
       <c r="B17" t="n">
-        <v>79648</v>
+        <v>90709</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2372,25 +2372,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229748</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2400,10 +2400,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545524</v>
+        <v>545532</v>
       </c>
       <c r="R17" t="n">
-        <v>7206894</v>
+        <v>7207020</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2472,10 +2472,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121072576</v>
+        <v>121072563</v>
       </c>
       <c r="B18" t="n">
-        <v>90662</v>
+        <v>77541</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2484,25 +2484,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545540</v>
+        <v>545530</v>
       </c>
       <c r="R18" t="n">
-        <v>7206902</v>
+        <v>7207027</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2584,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121072592</v>
+        <v>121072578</v>
       </c>
       <c r="B19" t="n">
-        <v>91630</v>
+        <v>78604</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2596,25 +2596,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545502</v>
+        <v>545524</v>
       </c>
       <c r="R19" t="n">
-        <v>7206865</v>
+        <v>7206893</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2696,10 +2696,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121072564</v>
+        <v>121072560</v>
       </c>
       <c r="B20" t="n">
-        <v>74708</v>
+        <v>78604</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2712,21 +2712,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2736,10 +2736,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545530</v>
+        <v>545571</v>
       </c>
       <c r="R20" t="n">
-        <v>7207028</v>
+        <v>7207020</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2808,10 +2808,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121072557</v>
+        <v>121072579</v>
       </c>
       <c r="B21" t="n">
-        <v>57351</v>
+        <v>79651</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2820,43 +2820,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>229748</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545608</v>
+        <v>545524</v>
       </c>
       <c r="R21" t="n">
-        <v>7206991</v>
+        <v>7206894</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2888,7 +2883,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2898,7 +2893,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2925,10 +2920,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121072551</v>
+        <v>121072565</v>
       </c>
       <c r="B22" t="n">
-        <v>91380</v>
+        <v>78604</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2937,25 +2932,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2965,10 +2960,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545676</v>
+        <v>545527</v>
       </c>
       <c r="R22" t="n">
-        <v>7206979</v>
+        <v>7207023</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3000,7 +2995,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3010,7 +3005,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3037,10 +3032,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121072554</v>
+        <v>121072561</v>
       </c>
       <c r="B23" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3077,10 +3072,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545672</v>
+        <v>545577</v>
       </c>
       <c r="R23" t="n">
-        <v>7206977</v>
+        <v>7207030</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3112,7 +3107,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3117,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3149,10 +3144,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121072580</v>
+        <v>121072573</v>
       </c>
       <c r="B24" t="n">
-        <v>79711</v>
+        <v>57351</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3161,38 +3156,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545525</v>
+        <v>545534</v>
       </c>
       <c r="R24" t="n">
-        <v>7206894</v>
+        <v>7206903</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3261,10 +3261,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121072587</v>
+        <v>121072585</v>
       </c>
       <c r="B25" t="n">
-        <v>94496</v>
+        <v>90723</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3273,25 +3273,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2813</v>
+        <v>1204</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>545516</v>
+        <v>545532</v>
       </c>
       <c r="R25" t="n">
-        <v>7206861</v>
+        <v>7206858</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3373,10 +3373,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121072556</v>
+        <v>121072577</v>
       </c>
       <c r="B26" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3413,10 +3413,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>545610</v>
+        <v>545540</v>
       </c>
       <c r="R26" t="n">
-        <v>7206991</v>
+        <v>7206902</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3485,10 +3485,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121072562</v>
+        <v>121072552</v>
       </c>
       <c r="B27" t="n">
-        <v>74713</v>
+        <v>78604</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3501,21 +3501,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3525,10 +3525,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>545531</v>
+        <v>545682</v>
       </c>
       <c r="R27" t="n">
-        <v>7207026</v>
+        <v>7206971</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3597,10 +3597,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121072593</v>
+        <v>121072574</v>
       </c>
       <c r="B28" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>545505</v>
+        <v>545534</v>
       </c>
       <c r="R28" t="n">
-        <v>7206860</v>
+        <v>7206903</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3672,7 +3672,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3709,10 +3709,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121072577</v>
+        <v>121072583</v>
       </c>
       <c r="B29" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>545540</v>
       </c>
       <c r="R29" t="n">
-        <v>7206902</v>
+        <v>7206882</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3821,10 +3821,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121072589</v>
+        <v>121072564</v>
       </c>
       <c r="B30" t="n">
-        <v>79711</v>
+        <v>74710</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3833,25 +3833,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>545508</v>
+        <v>545530</v>
       </c>
       <c r="R30" t="n">
-        <v>7206867</v>
+        <v>7207028</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3933,10 +3933,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121072567</v>
+        <v>121072586</v>
       </c>
       <c r="B31" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3973,10 +3973,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>545533</v>
+        <v>545532</v>
       </c>
       <c r="R31" t="n">
-        <v>7207012</v>
+        <v>7206858</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4045,10 +4045,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121072586</v>
+        <v>121072590</v>
       </c>
       <c r="B32" t="n">
-        <v>78601</v>
+        <v>94496</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4057,25 +4057,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4085,10 +4085,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>545532</v>
+        <v>545506</v>
       </c>
       <c r="R32" t="n">
-        <v>7206858</v>
+        <v>7206868</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4273,10 +4273,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121072566</v>
+        <v>121072570</v>
       </c>
       <c r="B34" t="n">
-        <v>90697</v>
+        <v>57462</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4285,38 +4285,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>545532</v>
+        <v>545597</v>
       </c>
       <c r="R34" t="n">
-        <v>7207020</v>
+        <v>7206943</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4348,7 +4352,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4358,7 +4362,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4385,10 +4389,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121072585</v>
+        <v>121072572</v>
       </c>
       <c r="B35" t="n">
-        <v>90711</v>
+        <v>78604</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4401,21 +4405,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4425,10 +4429,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>545532</v>
+        <v>545525</v>
       </c>
       <c r="R35" t="n">
-        <v>7206858</v>
+        <v>7206961</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4460,7 +4464,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4470,7 +4474,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4497,10 +4501,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121072560</v>
+        <v>121072587</v>
       </c>
       <c r="B36" t="n">
-        <v>78601</v>
+        <v>94508</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4509,25 +4513,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>2813</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4537,10 +4541,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>545571</v>
+        <v>545516</v>
       </c>
       <c r="R36" t="n">
-        <v>7207020</v>
+        <v>7206861</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4572,7 +4576,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4582,7 +4586,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4609,10 +4613,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121072569</v>
+        <v>121072557</v>
       </c>
       <c r="B37" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4625,34 +4629,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>545526</v>
+        <v>545608</v>
       </c>
       <c r="R37" t="n">
-        <v>7206990</v>
+        <v>7206991</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4684,7 +4693,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4694,7 +4703,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4721,10 +4730,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121072561</v>
+        <v>121072571</v>
       </c>
       <c r="B38" t="n">
-        <v>78601</v>
+        <v>77541</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4737,21 +4746,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4761,10 +4770,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>545577</v>
+        <v>545524</v>
       </c>
       <c r="R38" t="n">
-        <v>7207030</v>
+        <v>7206961</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4796,7 +4805,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4806,7 +4815,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4833,10 +4842,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121072574</v>
+        <v>121072554</v>
       </c>
       <c r="B39" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4873,10 +4882,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>545534</v>
+        <v>545672</v>
       </c>
       <c r="R39" t="n">
-        <v>7206903</v>
+        <v>7206977</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4908,7 +4917,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4918,7 +4927,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4945,10 +4954,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121072573</v>
+        <v>121072593</v>
       </c>
       <c r="B40" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4961,39 +4970,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>545534</v>
+        <v>545505</v>
       </c>
       <c r="R40" t="n">
-        <v>7206903</v>
+        <v>7206860</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5025,7 +5029,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5035,7 +5039,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5062,10 +5066,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121072570</v>
+        <v>121072580</v>
       </c>
       <c r="B41" t="n">
-        <v>57462</v>
+        <v>79714</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5078,38 +5082,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103031</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bladberget, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>545597</v>
+        <v>545525</v>
       </c>
       <c r="R41" t="n">
-        <v>7206943</v>
+        <v>7206894</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5178,10 +5178,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121072591</v>
+        <v>121072582</v>
       </c>
       <c r="B42" t="n">
-        <v>97035</v>
+        <v>74708</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5190,25 +5190,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>6486</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5218,10 +5218,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>545503</v>
+        <v>545540</v>
       </c>
       <c r="R42" t="n">
-        <v>7206867</v>
+        <v>7206883</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD42" t="b">
